--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +84,12 @@
       <color rgb="00166534"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -133,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -155,11 +161,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -210,6 +260,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -828,9 +886,9 @@
           <t>आयु गिनने का तरीका ⭐</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>🔴 बाकी — दशा एक वर्ष खिसक सकती है</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — जीवन-वर्ष वाली गिनती सही (Completed Age 0–5)। जो लगाया था वही सही।</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -840,7 +898,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>क या ख चुनें</t>
+          <t>कुछ नहीं</t>
         </is>
       </c>
     </row>
@@ -882,9 +940,9 @@
           <t>मसनूई तालिका</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🟠 बाकी — न मिले तो सुविधा बंद रहेगी</t>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>✅ तालिका मिल गई (12 जोड़ियाँ) — पर 2 टकराव हैं, स्पष्टीकरण चाहिए।</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -894,7 +952,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>जितना पता हो</t>
+          <t>2 टकराव सुलझाएँ</t>
         </is>
       </c>
     </row>
@@ -1276,6 +1334,14 @@
           <t>✅ आपके सवाल का सीधा उत्तर: हाँ — मेरे पास (1) हर ग्रह का उच्च घर, और (2) कारक भाव — दोनों अलग-अलग मौजूद हैं। इन्हीं से नीचे मिलान किया है।</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="20" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1283,6 +1349,14 @@
           <t>⚠️ प्रमाण — आपकी दी हुई 'पक्का घर' सूची में तीनों चीज़ें मिली हुई हैं: गुरु की पूरी सूची (2,5,9,11) हूबहू कारक-भाव है · केतु की सूची (9) केवल उच्च घर है · चन्द्र की सूची = उच्च (2) + कारक (4)। यानी शुद्ध 'पक्का घर' अलग से चाहिए।</t>
         </is>
       </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="20" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1652,6 +1726,14 @@
           <t>❗ दूसरी समस्या (नई मिली): सॉफ़्टवेयर में अब तक जो 'पक्का घर' तालिका थी, वह असल में कारक-भाव की नकल थी — 9 में से 7 ग्रहों पर हूबहू वही, बाकी 2 उसका हिस्सा। यानी सॉफ़्टवेयर 'कारक भाव' को 'पक्का घर' कहता रहा है।</t>
         </is>
       </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="20" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -1659,6 +1741,14 @@
           <t>मुझे आपसे यही चाहिए — तीनों सूचियाँ अलग-अलग (नीचे भरें या पुष्टि करें)</t>
         </is>
       </c>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="20" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -2001,6 +2091,14 @@
           <t>आपने पूछा था 'प्रत्येक भाव का कारक कौन सा ग्रह है' — ऊपर वाली तालिका मेरे डेटा से बनी है। यदि इसमें कोई भाव गलत है तो ✏️ वाले खाने में सही ग्रह लिख दें। इसके बाद ऊपर की तालिका में केवल शुद्ध पक्का/कच्चा घर भर दें — तब गणना ठीक हो जाएगी।</t>
         </is>
       </c>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2045,6 +2143,10 @@
           <t>① मुख्य दशा — 35-साला ग्रह-चक्र (स्थिर व सार्वभौमिक; जन्म से; 1–35, 36–70, 71–105 … दोहराव)</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="20" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2267,6 +2369,10 @@
           <t>⚠️ grah_chakra का 'प्रभाव' कॉलम इसी चक्र की भ्रष्ट प्रति है (शनि पीछे घुमाया, राहु 6→4) — समय हेतु प्रयोग न करें।</t>
         </is>
       </c>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="20" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -2274,6 +2380,10 @@
           <t>② मियाद — जीवन-पड़ाव (रैखिक प्राकृतिक विकास; चक्र नहीं — बचपन/जवानी लौटकर नहीं आती)</t>
         </is>
       </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="20" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -2556,6 +2666,10 @@
           <t>✔ सवाल 4 का उत्तर: 'शुक्र ही जीवन-भर'। यह दशा-चक्र की तरह घूमने वाला चक्र नहीं — यह रैखिक प्राकृतिक विकास है, इसलिए सूर्य से दोबारा शुरू नहीं होता।</t>
         </is>
       </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="20" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -2563,6 +2677,10 @@
           <t>③ अवस्था — कुण्डली के 4 टाइम-ज़ोन (भाव = 'जीवन की घड़ियाँ')</t>
         </is>
       </c>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="20" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -2697,6 +2815,10 @@
           <t>⭐ केंद्र-बिंदु: जिस अवस्था में सर्वाधिक ग्रह — जीवन की सबसे बड़ी घटनाएँ उसी खंड में (peak time)।</t>
         </is>
       </c>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="20" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -2704,6 +2826,10 @@
           <t>😴 खाली अवस्था: तीनों भाव खाली ⇒ वे 25 वर्ष रूटीन (autopilot) में शांति से बीतेंगे।</t>
         </is>
       </c>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2749,6 +2875,10 @@
           <t>आपका नियम: यदि कुंडली में कोई ग्रह सोया हुआ है और फल नहीं दे रहा, तो वह तालिका में दी गई आयु पर स्वतः (अपने आप) सक्रिय हो जाता है — तब उसे जगाने के उपाय की ज़रूरत नहीं होती।</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="20" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
@@ -2756,6 +2886,10 @@
           <t>⚙️ इंजन पर असर: 'जागृति-उपाय' अब हर सोए ग्रह पर नहीं दिया जाएगा। उसकी जगह यह बताया जाएगा कि ग्रह किस आयु पर स्वयं जागेगा। (उपाय केवल तभी जब कोई और कारण हो — जैसे पाप-युति या कच्चा घर।)</t>
         </is>
       </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="20" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -3178,7 +3312,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>F1</t>
@@ -3199,8 +3333,16 @@
           <t>(क) जीवन-वर्ष — नवजात 'वर्ष 1' में</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✅ उत्तर मिला — (क) सही</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>जीवन का 1st वर्ष = जन्म→पहला जन्मदिन = Completed Age 0। शनि 1–6 वर्ष = Completed Age 0–5। यही मैंने लगाया था — बदलाव नहीं चाहिए।</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -3312,7 +3454,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>फल / टिप्पणी</t>
+          <t>टिप्पणी / टकराव</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -3354,207 +3496,356 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>मंगल (नेक)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ टकराव — पंक्ति 5 भी सूर्य+बुध है</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>मंगल (बद)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ टकराव — पंक्ति 10 भी सूर्य+शनि है</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ टकराव — पंक्ति 2 भी सूर्य+बुध है</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>शनि (केतु-स्वभाव)</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>शनि (राहु-स्वभाव)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>राहु (उच्च)</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>राहु (नीच)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ टकराव — पंक्ति 3 भी सूर्य+शनि है; दस्तावेज़ से मेल खाती है</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="8" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>केतु (उच्च)</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="8" t="inlineStr"/>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>केतु (नीच)</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ दो टकराव: सूर्य+बुध (पंक्ति 2 व 5) और सूर्य+शनि (पंक्ति 3 व 10) — एक ही जोड़ी के दो नतीजे। क्या कोई अतिरिक्त शर्त है, या टाइपिंग की गलती?</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr"/>
-      <c r="D23" s="8" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="8" t="inlineStr"/>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -3595,6 +3886,9 @@
           <t>विकल्प 1 (सुझाया): प्रतिशत की ज़रूरत नहीं — आपकी xlsx की bhav_drishti शीट में पहले से neev (=बुनियाद), takrav (=टक्कर), sahayak व vishwasghat कॉलम हैं।</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="20" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">

--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="STATUS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PAKKA_ANALYSIS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ANSWERED_A2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ANSWERED_SUPT" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="A_Pending" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Followups" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Masnui" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Drishti_Pct" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="B_C_Confirm" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Scope" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ANSWERED_UCHNEECH" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ANSWERED_A2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ANSWERED_SUPT" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="A_Pending" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Followups" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Masnui" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Drishti_Pct" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="B_C_Confirm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Scope" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +89,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -209,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -268,6 +275,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -635,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1064,6 +1077,33 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>उच्च / नीच के ग्रह</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — भाव-अनुसार दोनों सूचियाँ मिल गईं। 7 ग्रह मेरे डेटा से मेल; राहु-केतु में एक-एक भाव और जुड़ा।</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ANSWERED_UCHNEECH</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>एक छोटी पुष्टि (राहु नीच 8 या 12)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
@@ -1074,6 +1114,305 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🟡 12 नियम — असली पुष्टि बाकी</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>पिछली बार AI ने मेरे ही प्रस्ताव लौटा दिए थे। तब तक ये 'अनुमानित' चिह्नित रहेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Q#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>विषय</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>मेरा नियम (अभी लागू)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>पुष्टि?</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>सुधार</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>धोखा दृष्टि</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>सहायक/नींव दृष्टि, पर दृष्टि डालने वाला ग्रह स्वयं पीड़ित या भाव-स्वामी का शत्रु</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>बलि का बकरा</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>कच्चे घर का पीड़ित पाप ग्रह जो कायम शुभ ग्रह/लग्न की पीड़ा सोख रहा हो (उपाय न करें)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>अंधी कुंडली</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>≤3 भावों में ग्रह ⇒ अंधी · 4–5 ⇒ आधी अंधी · 6+ ⇒ सामान्य</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>मुकाबले के ग्रह</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>karak_bhav साझा + maitri में शत्रुता</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>किस्मत जगाने वाला</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>सबसे बलवान कायम शुभ ग्रह जो 9/10/11 से जुड़ा</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>गूंगा ग्रह</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>दोनों पड़ोसी भावों में पाप या पाप-दृष्टि, कोई शुभ दृष्टि नहीं</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>मृत ग्रह</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>गूंगा + बहरा + अंधा — तीनों एक साथ</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>बहरा ग्रह</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>कोई शुभ दृष्टि नहीं + कच्चा घर + भाव-स्वामी भी पीड़ित</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>गूंगा मकान vs सोया घर</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>सोया = अस्थायी · गूंगा = स्थायी रूप से मूक</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>अंधा ग्रह</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>न शुभ दृष्टि, न पाप दृष्टि, न साथी — कोई संपर्क नहीं</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>सवा-मात्रा</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ठोस ⇒ सवा किलो · धन ⇒ सवा नौ/इक्यावन · वस्त्र ⇒ सवा मीटर</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>राशि परिवर्तन</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>गोचर/वर्षफल में वर्तमान राशि; लाल किताब भाव जन्म-अनुसार स्थिर</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"सही है,बदलें,पता नहीं"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1419,8 +1758,10 @@
           <t>1, 9, 10</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>1</v>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -1454,8 +1795,10 @@
           <t>2, 4</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>2</v>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1469,7 +1812,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>— कुछ नहीं बचा</t>
+          <t>— कुछ नहीं</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
@@ -1489,8 +1832,10 @@
           <t>1, 8, 11</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>10</v>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -1524,8 +1869,10 @@
           <t>2, 5, 6</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>6</v>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -1559,8 +1906,10 @@
           <t>2, 5, 9, 11</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>4</v>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -1574,7 +1923,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>— कुछ नहीं बचा</t>
+          <t>— कुछ नहीं</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
@@ -1594,8 +1943,10 @@
           <t>4, 7, 12</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>12</v>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1629,8 +1980,10 @@
           <t>3, 7, 10, 11</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
-        <v>7</v>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -1664,8 +2017,10 @@
           <t>3, 6, 11</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>3</v>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>3, 6</t>
+        </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
@@ -1674,12 +2029,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>3=उच्च · 6=?? · 11=??</t>
+          <t>3=उच्च · 6=उच्च · 11=??</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>6, 11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr"/>
@@ -1699,8 +2054,10 @@
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>9</v>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>9, 12</t>
+        </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
@@ -1714,12 +2071,13 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>— कुछ नहीं बचा</t>
+          <t>— कुछ नहीं</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -1735,6 +2093,13 @@
       <c r="H18" s="19" t="n"/>
       <c r="I18" s="20" t="n"/>
     </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>🔄 अद्यतन: उच्च-घर कॉलम अब आपकी नई सूची से है (राहु 3,6 · केतु 9,12)। इससे राहु की 'पक्का' सूची में अब केवल भाव 11 बचता है — यानी मिश्रण और भी साफ़ दिखता है।</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
@@ -1921,7 +2286,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>बुध</t>
+          <t>बुध, राहु</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -2071,7 +2436,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>शुक्र</t>
+          <t>शुक्र, केतु</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -2085,6 +2450,7 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr"/>
     </row>
+    <row r="34"/>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
@@ -2101,8 +2467,9 @@
       <c r="I35" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A18:I18"/>
@@ -2120,6 +2487,764 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>✅ उच्च व नीच के ग्रह — आपकी दी सूचियाँ (दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>① भाव-अनुसार (आपने इसी रूप में दिया)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>भाव</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>उच्च के ग्रह</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>नीच के ग्रह</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>भाव 1</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>भाव 2</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>भाव 3</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>भाव 4</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>भाव 5</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>भाव 6</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>बुध और राहु</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>शुक्र और केतु</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>भाव 7</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>भाव 8</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>चन्द्र और राहु</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>भाव 9</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>भाव 10</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>भाव 11</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>भाव 12</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र और केतु</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>② ग्रह-अनुसार (मैंने पलटकर बनाया) — और मेरे पुराने डेटा से मिलान</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ग्रह</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>उच्च (आपका)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>नीच (आपका)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>उच्च (मेरा पुराना)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>नीच (मेरा पुराना)</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>मिलान</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>✓ पूरी तरह मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>3, 6</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>8, 9</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>🔵 नया भाव जुड़ा — मेरा डेटा अधूरा था</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>9, 12</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>3, 6</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>🔵 नया भाव जुड़ा — मेरा डेटा अधूरा था</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>✔ नतीजा: 7 ग्रहों पर आपकी सूची मेरे डेटा से हूबहू मिलती है। केवल राहु व केतु में एक-एक भाव और जुड़ा — मेरा डेटा वहाँ अधूरा था। अब पूरा हो गया।</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>🔍 एक छोटी जाँच (केवल पुष्टि हेतु — गलती नहीं कह रहा)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>राहु-केतु आमने-सामने के ग्रह हैं, इसलिए इनमें आईने जैसा क्रम दिखता है:
+• राहु उच्च 3, 6  ↔  केतु उच्च 9, 12 (ठीक सामने वाले भाव) ✓
+• राहु उच्च 3, 6  =  केतु नीच 3, 6 (जहाँ एक उच्च, वहीं दूसरा नीच) ✓
+• केतु उच्च 9, 12  →  इस नियम से राहु नीच 9, 12 बनता; पर आपने राहु नीच 8, 9 दिया — 9 मेल खाता है, 12 की जगह 8 है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>प्रश्न</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>राहु नीच में 8 है या 12? (या दोनों?)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>✏️ आपका उत्तर:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>यदि 8 ही सही है तो कोई बात नहीं — केवल पक्का करना चाहता था, क्योंकि बाकी तीनों जगह आईना पूरा बैठता है।</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A33:G33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2846,7 +3971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3099,7 +4224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3256,7 +4381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3400,7 +4525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3858,7 +4983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4080,303 +5205,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>🟡 12 नियम — असली पुष्टि बाकी</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>पिछली बार AI ने मेरे ही प्रस्ताव लौटा दिए थे। तब तक ये 'अनुमानित' चिह्नित रहेंगे।</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Q#</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>विषय</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>मेरा नियम (अभी लागू)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>पुष्टि?</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>सुधार</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>धोखा दृष्टि</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>सहायक/नींव दृष्टि, पर दृष्टि डालने वाला ग्रह स्वयं पीड़ित या भाव-स्वामी का शत्रु</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>बलि का बकरा</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>कच्चे घर का पीड़ित पाप ग्रह जो कायम शुभ ग्रह/लग्न की पीड़ा सोख रहा हो (उपाय न करें)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>अंधी कुंडली</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>≤3 भावों में ग्रह ⇒ अंधी · 4–5 ⇒ आधी अंधी · 6+ ⇒ सामान्य</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>मुकाबले के ग्रह</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>karak_bhav साझा + maitri में शत्रुता</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>किस्मत जगाने वाला</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>सबसे बलवान कायम शुभ ग्रह जो 9/10/11 से जुड़ा</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>गूंगा ग्रह</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>दोनों पड़ोसी भावों में पाप या पाप-दृष्टि, कोई शुभ दृष्टि नहीं</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>मृत ग्रह</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>गूंगा + बहरा + अंधा — तीनों एक साथ</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>बहरा ग्रह</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>कोई शुभ दृष्टि नहीं + कच्चा घर + भाव-स्वामी भी पीड़ित</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>गूंगा मकान vs सोया घर</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>सोया = अस्थायी · गूंगा = स्थायी रूप से मूक</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>अंधा ग्रह</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>न शुभ दृष्टि, न पाप दृष्टि, न साथी — कोई संपर्क नहीं</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>सवा-मात्रा</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>ठोस ⇒ सवा किलो · धन ⇒ सवा नौ/इक्यावन · वस्त्र ⇒ सवा मीटर</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>राशि परिवर्तन</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>गोचर/वर्षफल में वर्तमान राशि; लाल किताब भाव जन्म-अनुसार स्थिर</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D5:D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"सही है,बदलें,पता नहीं"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -12,12 +12,13 @@
     <sheet name="ANSWERED_UCHNEECH" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ANSWERED_A2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ANSWERED_SUPT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="A_Pending" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Followups" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Masnui" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Drishti_Pct" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="B_C_Confirm" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Scope" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ANSWERED_SOYA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="A_Pending" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Followups" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Masnui" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Drishti_Pct" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="B_C_Confirm" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Scope" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -146,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -212,11 +213,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -283,6 +285,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -648,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -847,12 +862,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>🔴 बाकी — 'कौन सा ग्रह सोया है' यह किस नियम से तय हो? (क्या करना है, वह तय हो गया)</t>
+          <t>🟡 आधा तय — 'सोया भाव' की परिभाषा मिल गई। बाकी: 'सोया ग्रह' अलग है क्या, और दृष्टि किस प्रणाली से?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>A_Pending</t>
+          <t>ANSWERED_SOYA</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -953,9 +968,9 @@
           <t>मसनूई तालिका</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>✅ तालिका मिल गई (12 जोड़ियाँ) — पर 2 टकराव हैं, स्पष्टीकरण चाहिए।</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>🟡 लगभग पूरी — सूर्य+बुध=मंगल तय, नई जोड़ी सूर्य+शुक्र=गुरु मिली। बचा: सूर्य+शनि का टकराव।</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -965,7 +980,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2 टकराव सुलझाएँ</t>
+          <t>1 टकराव बचा</t>
         </is>
       </c>
     </row>
@@ -1101,6 +1116,87 @@
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>एक छोटी पुष्टि (राहु नीच 8 या 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>उच्च/नीच सुधार</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>✅ राहु नीच 9,12 (पहले 8,9) · केतु नीच 3,6 — आईना अब पूरा।</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ANSWERED_UCHNEECH</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>कुछ नहीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>सोया भाव</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>✅ परिभाषा मिल गई — खाली भाव + कोई दृष्टि नहीं।</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ANSWERED_SOYA</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2 उप-सवाल</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>दशा-सीमा</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>✅ शनि 1–6 = 5 वर्ष 11 माह 29 दिन; छठे जन्मदिन पर राहु शुरू। जो लगा है वही सही।</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ANSWERED_A2</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>कुछ नहीं</t>
         </is>
       </c>
     </row>
@@ -1114,6 +1210,230 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🟠 दृष्टि — आसान विकल्प मौजूद</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>विकल्प 1 (सुझाया): प्रतिशत की ज़रूरत नहीं — आपकी xlsx की bhav_drishti शीट में पहले से neev (=बुनियाद), takrav (=टक्कर), sahayak व vishwasghat कॉलम हैं।</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="20" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>→</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>आपका निर्णय:</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>☐ 'bhav_drishti का उपयोग करो' लिखें, या नीचे प्रतिशत भरें</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>दूरी</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>अर्थ</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>प्रतिशत</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>टिप्पणी</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>अगला भाव (2रा)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>3रा</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>4था</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>5वाँ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>6ठा</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>7वाँ (सामने)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>आपने पहले भरा</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>8वाँ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>9वाँ</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>10वाँ</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>11वाँ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>12वाँ</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"100,50,25,0"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1412,7 +1732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2077,7 +2397,6 @@
       <c r="H16" s="8" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2099,6 +2418,14 @@
           <t>🔄 अद्यतन: उच्च-घर कॉलम अब आपकी नई सूची से है (राहु 3,6 · केतु 9,12)। इससे राहु की 'पक्का' सूची में अब केवल भाव 11 बचता है — यानी मिश्रण और भी साफ़ दिखता है।</t>
         </is>
       </c>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="20" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -2450,7 +2777,6 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr"/>
     </row>
-    <row r="34"/>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
@@ -2487,7 +2813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2512,6 +2838,12 @@
           <t>① भाव-अनुसार (आपने इसी रूप में दिया)</t>
         </is>
       </c>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="n"/>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="19" t="n"/>
+      <c r="G3" s="20" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2713,9 +3045,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>चन्द्र और राहु</t>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2805,9 +3137,9 @@
           <t>शुक्र और केतु</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>बुध</t>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>बुध और राहु</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2820,6 +3152,12 @@
           <t>② ग्रह-अनुसार (मैंने पलटकर बनाया) — और मेरे पुराने डेटा से मिलान</t>
         </is>
       </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="20" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -3117,9 +3455,9 @@
           <t>3, 6</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>8, 9</t>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>9, 12</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -3134,7 +3472,7 @@
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>🔵 नया भाव जुड़ा — मेरा डेटा अधूरा था</t>
+          <t>🔵 सुधारा — आईना अब पूरा</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3490,7 @@
           <t>9, 12</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>3, 6</t>
         </is>
@@ -3169,23 +3507,37 @@
       </c>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>🔵 नया भाव जुड़ा — मेरा डेटा अधूरा था</t>
-        </is>
-      </c>
-    </row>
+          <t>🔵 सुधारा — आईना अब पूरा</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>✔ नतीजा: 7 ग्रहों पर आपकी सूची मेरे डेटा से हूबहू मिलती है। केवल राहु व केतु में एक-एक भाव और जुड़ा — मेरा डेटा वहाँ अधूरा था। अब पूरा हो गया।</t>
         </is>
       </c>
-    </row>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="20" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
           <t>🔍 एक छोटी जाँच (केवल पुष्टि हेतु — गलती नहीं कह रहा)</t>
         </is>
       </c>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="20" t="n"/>
     </row>
     <row r="33" ht="64" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
@@ -3196,6 +3548,12 @@
 • केतु उच्च 9, 12  →  इस नियम से राहु नीच 9, 12 बनता; पर आपने राहु नीच 8, 9 दिया — 9 मेल खाता है, 12 की जगह 8 है।</t>
         </is>
       </c>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="20" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="5" t="inlineStr"/>
@@ -3224,16 +3582,38 @@
           <t>यदि 8 ही सही है तो कोई बात नहीं — केवल पक्का करना चाहता था, क्योंकि बाकी तीनों जगह आईना पूरा बैठता है।</t>
         </is>
       </c>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="20" t="n"/>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>🔄 सुधार दर्ज: राहु नीच = 9, 12 (पहले 8, 9) · केतु नीच = 3, 6। अब आईना पूरा — जहाँ राहु उच्च (3, 6) वहीं केतु नीच; जहाँ केतु उच्च (9, 12) वहीं राहु नीच। भाव-सूची में असर: भाव 8 से राहु हटा, भाव 12 में राहु जुड़ा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>✔ मेरी पिछली जाँच सही निकली — 8 की जगह 12 ही था।</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3245,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3956,13 +4336,29 @@
       <c r="D39" s="19" t="n"/>
       <c r="E39" s="20" t="n"/>
     </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>🎯 दशा-सीमा की सटीक परिभाषा: शनि '1 से 6 वर्ष' = जन्म से छठे जन्मदिन से ठीक एक दिन पहले तक — यानी 5 वर्ष 11 महीने 29 दिन। जिस दिन छठा जन्मदिन आता है, उसी दिन 7वाँ वर्ष शुरू होकर राहु दशा (7–12) लग जाती है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>✔ यही गणना पहले से लगी है (जीवन-वर्ष = पूर्ण आयु + 1) — कोई बदलाव नहीं चाहिए।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A18:E18"/>
@@ -4230,6 +4626,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>✅ सोया भाव (घर) — परिभाषा मिल गई</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>आपका नियम: यदि कोई भाव पूरी तरह खाली हो (कोई ग्रह न बैठा हो) और उस भाव पर किसी अन्य ग्रह की दृष्टि भी न पड़ रही हो — तो वह 'सोया हुआ भाव' है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>⚙️ यह गणना-योग्य है — दो शर्तें: (1) भाव खाली · (2) उस पर कोई दृष्टि नहीं।</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>❓ इससे जुड़े दो सवाल</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>सवाल</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>विवरण</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>✏️ आपका उत्तर</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>कौन सी दृष्टि गिनें?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>'किसी अन्य ग्रह की दृष्टि' — किस दृष्टि-प्रणाली से? आपकी xlsx की bhav_drishti शीट (drishti / neev / takrav / sahayak कॉलम) से, या कोई और? यह वही सवाल है जो दृष्टि-प्रतिशत वाला था — एक उत्तर से दोनों सुलझ जाएँगे।</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>'सोया ग्रह' अलग है?</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>आपने 'सोया भाव' बता दिया ✅ — पर A3 का सवाल 'सोया ग्रह' का था (जो ग्रह किसी भाव में बैठा है पर फल नहीं दे रहा)। क्या लाल किताब में 'सोया ग्रह' अलग चीज़ है, या केवल 'सोया भाव' देखा जाता है?</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4307,12 +4811,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>सोया ग्रह — कैसे पहचानें</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>यह अब भी बाकी है: 'कौन सा ग्रह सोया है' यह किस नियम से तय हो? (क्या करना है — वह आपने बता दिया: वह स्वतः जागेगा।)</t>
+          <t>सोया भाव ✅ / सोया ग्रह 🔴</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>✅ 'सोया भाव' मिल गया (खाली + कोई दृष्टि नहीं) — शीट ANSWERED_SOYA। 🔴 बाकी: क्या 'सोया ग्रह' अलग चीज़ है? और दृष्टि किस प्रणाली से गिनें?</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4381,7 +4885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4525,7 +5029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4579,7 +5083,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>टिप्पणी / टकराव</t>
+          <t>स्थिति</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -4589,232 +5093,246 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>EX</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>सूर्य</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>कृत्रिम राहु</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>दस्तावेज़ का उदाहरण — रहने दें</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
           <t>बुध</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>✅ टकराव सुलझा — यही मसनुई मंगल है</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>शुक्र</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="14" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>✅ सुधार — पहले 'सूर्य+बुध' लिखा था; सही है सूर्य+शुक्र</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>बुध</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>मंगल (नेक)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ टकराव — पंक्ति 5 भी सूर्य+बुध है</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>मंगल (बद)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ टकराव — पंक्ति 10 भी सूर्य+शनि है</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
           <t>गुरु</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>राहु</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>बुध</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>बुध</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>गुरु</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ टकराव — पंक्ति 2 भी सूर्य+बुध है</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>शनि (केतु-स्वभाव)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>राहु</t>
+          <t>मंगल</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>केतु</t>
+          <t>बुध</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+          <t>शनि (राहु-स्वभाव)</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>शुक्र</t>
+          <t>मंगल</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>गुरु</t>
+          <t>शनि</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>शनि (केतु-स्वभाव)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+          <t>राहु (उच्च)</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>मंगल</t>
+          <t>शनि</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>बुध</t>
+          <t>शुक्र</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>शनि (राहु-स्वभाव)</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
+          <t>केतु (उच्च)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>मंगल</t>
+          <t>चन्द्र</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -4824,15 +5342,19 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>राहु (उच्च)</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
+          <t>केतु (नीच)</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4846,133 +5368,100 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>राहु (नीच)</t>
+          <t>मंगल (बद)  ⟷  राहु (नीच)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>⚠️ टकराव — पंक्ति 3 भी सूर्य+शनि है; दस्तावेज़ से मेल खाती है</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr"/>
+          <t>🔴 अब भी टकराव — कौन सा सही?</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>केतु (उच्च)</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>चन्द्र</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>केतु (नीच)</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>🔴 बचा हुआ एक टकराव — सूर्य + शनि: आपने पहले 'मंगल (बद)' भी लिखा था और 'राहु (नीच)' भी। आपके नियम-दस्तावेज़ में 'सूर्य + शनि = कृत्रिम राहु' लिखा है, जो 'राहु (नीच)' से मेल खाता है। कृपया बताएँ — कौन सा सही है, या दोनों की अलग-अलग शर्त है?</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ दो टकराव: सूर्य+बुध (पंक्ति 2 व 5) और सूर्य+शनि (पंक्ति 3 व 10) — एक ही जोड़ी के दो नतीजे। क्या कोई अतिरिक्त शर्त है, या टाइपिंग की गलती?</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="20" t="n"/>
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4981,228 +5470,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>🟠 दृष्टि — आसान विकल्प मौजूद</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>विकल्प 1 (सुझाया): प्रतिशत की ज़रूरत नहीं — आपकी xlsx की bhav_drishti शीट में पहले से neev (=बुनियाद), takrav (=टक्कर), sahayak व vishwasghat कॉलम हैं।</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="20" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>→</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>आपका निर्णय:</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>☐ 'bhav_drishti का उपयोग करो' लिखें, या नीचे प्रतिशत भरें</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>दूरी</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>अर्थ</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>प्रतिशत</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>टिप्पणी</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>अगला भाव (2रा)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>3रा</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>4था</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>5वाँ</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>6ठा</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>7वाँ (सामने)</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>आपने पहले भरा</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>8वाँ</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>9वाँ</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>10वाँ</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>11वाँ</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>12वाँ</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C8:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"100,50,25,0"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>🟡 आधा तय — 'सोया भाव' की परिभाषा मिल गई। बाकी: 'सोया ग्रह' अलग है क्या, और दृष्टि किस प्रणाली से?</t>
+          <t>🟡 दोनों परिभाषाएँ मिलीं (सोया भाव व सोया ग्रह) — बाकी: भाव जगाने की चाबी-तालिका।</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -968,9 +968,9 @@
           <t>मसनूई तालिका</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>🟡 लगभग पूरी — सूर्य+बुध=मंगल तय, नई जोड़ी सूर्य+शुक्र=गुरु मिली। बचा: सूर्य+शनि का टकराव।</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>✅ पूरी — सूर्य+शनि = मंगल बद (असर नीच राहु जैसा)। सारे टकराव सुलझे।</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1 टकराव बचा</t>
+          <t>कुछ नहीं</t>
         </is>
       </c>
     </row>
@@ -995,9 +995,9 @@
           <t>दृष्टि प्रतिशत</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>🟠 बाकी — आसान विकल्प मौजूद</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>🟡 नियम मिल गए (प्रतिशत सहित) — पर शीट से 3 टकराव; 5 भावों का ज़िक्र नहीं।</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>एक पंक्ति</t>
+          <t>3 उप-सवाल</t>
         </is>
       </c>
     </row>
@@ -1215,13 +1215,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1231,198 +1231,343 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>विकल्प 1 (सुझाया): प्रतिशत की ज़रूरत नहीं — आपकी xlsx की bhav_drishti शीट में पहले से neev (=बुनियाद), takrav (=टक्कर), sahayak व vishwasghat कॉलम हैं।</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="20" t="n"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>✅ आपके दिए नियम (दर्ज) — दृष्टि एकतरफ़ा, आगे की ओर; पीछे नहीं देखती (8→2 अपवाद छोड़कर)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>भाव</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>किसे देखता है</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>प्रतिशत</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>xlsx शीट / मिलान</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>→</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>आपका निर्णय:</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>☐ 'bhav_drishti का उपयोग करो' लिखें, या नीचे प्रतिशत भरें</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>7 ✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>8 ✗ अलग</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>दूरी</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>अर्थ</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>प्रतिशत</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>टिप्पणी</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>9, 11</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>9 ◐ आंशिक</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>10 ✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>11 ✗ अलग</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>12 ✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>100% (उल्टी/टक्कर)</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>2 ✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7, 9, 10, 11, 12</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>— आपके नियम में नहीं</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>शीट में +6 वाला भाव</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>🔎 xlsx का drishti कॉलम सीधा गणित है — हर भाव अपने से 6 आगे वाले को देखता है। न प्रतिशत, न अपवाद।</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ 3 टकराव — भाव 2 (आप 6 / शीट 8) · भाव 5 (आप 9 / शीट 11) · भाव 3 (आप 9+11 / शीट केवल 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>सवाल</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>विवरण</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>✏️ आपका उत्तर</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>सूची पूरी है?</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>भाव 7, 9, 10, 11, 12 — क्या ये किसी को नहीं देखते?</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>अगला भाव (2रा)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>बुनियाद की पूरी सूची</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>आपने दो दिए: 9→5 की बुनियाद · 2→8 की बुनियाद। और जोड़े?</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>3रा</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>4था</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>5वाँ</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>6ठा</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>7वाँ (सामने)</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>आपने पहले भरा</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>8वाँ</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>9वाँ</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>10वाँ</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>11वाँ</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>12वाँ</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>टकराव में किसे मानें</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>जहाँ आपका नियम व शीट अलग — हमेशा आपका नियम सही मानूँ?</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C8:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3511,7 +3656,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
@@ -3525,7 +3669,6 @@
       <c r="F30" s="19" t="n"/>
       <c r="G30" s="20" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
@@ -3595,6 +3738,12 @@
           <t>🔄 सुधार दर्ज: राहु नीच = 9, 12 (पहले 8, 9) · केतु नीच = 3, 6। अब आईना पूरा — जहाँ राहु उच्च (3, 6) वहीं केतु नीच; जहाँ केतु उच्च (9, 12) वहीं राहु नीच। भाव-सूची में असर: भाव 8 से राहु हटा, भाव 12 में राहु जुड़ा।</t>
         </is>
       </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="20" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -3602,6 +3751,12 @@
           <t>✔ मेरी पिछली जाँच सही निकली — 8 की जगह 12 ही था।</t>
         </is>
       </c>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4342,6 +4497,10 @@
           <t>🎯 दशा-सीमा की सटीक परिभाषा: शनि '1 से 6 वर्ष' = जन्म से छठे जन्मदिन से ठीक एक दिन पहले तक — यानी 5 वर्ष 11 महीने 29 दिन। जिस दिन छठा जन्मदिन आता है, उसी दिन 7वाँ वर्ष शुरू होकर राहु दशा (7–12) लग जाती है।</t>
         </is>
       </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="20" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
@@ -4349,6 +4508,10 @@
           <t>✔ यही गणना पहले से लगी है (जीवन-वर्ष = पूर्ण आयु + 1) — कोई बदलाव नहीं चाहिए।</t>
         </is>
       </c>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4626,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4717,12 +4880,231 @@
       </c>
       <c r="D9" s="8" t="inlineStr"/>
     </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>✅ सोया ग्रह — परिभाषा</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ग्रह भाव में बैठा है, पर जिस भाव को देखना चाहिए वह पूरी तरह खाली ⇒ सोया। उदा: सूर्य 1st में, 7th खाली ⇒ सूर्य सोया। असर: कोई फल नहीं — न अच्छा न बुरा। जागता है: ① उम्र से (शनि 36, राहु 42) ② कर्म से (नींव⇒शनि, विवाह⇒शुक्र)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>🔗 यह दृष्टि पर निर्भर है — दृष्टि का सवाल हल होते ही यह नियम चालू हो जाएगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>🔴 चाहिए — सोया भाव जगाने की 'चाबी' तालिका</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>सोया भाव</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>जगाने वाला भाव (चाबी)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>स्थिति</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>भाव 1</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>भाव 2</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>भाव 3</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>भाव 4</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>भाव 5</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>भाव 6</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>भाव 7</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>भाव 8</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>भाव 9 (भाग्य)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>भाव 2 (धर्मस्थान/कुटुंब)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>✅ आपने बताया</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>भाव 10</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>भाव 11</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>भाव 12</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>चाहिए</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5353,27 +5735,27 @@
       <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>सूर्य</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>शनि</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>मंगल (बद)  ⟷  राहु (नीच)</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>🔴 अब भी टकराव — कौन सा सही?</t>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>मंगल (बद)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — फलादेश में 'नीच राहु' जैसा असर</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -5393,13 +5775,12 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>✅ मसनूई तालिका पूरी — सूर्य+शनि = मंगल बद (फल नीच राहु जैसा)। दस्तावेज़ का 'सूर्य+शनि = कृत्रिम राहु' वाला कथन असर की बात था, नाम की नहीं।</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="27" t="n"/>
@@ -5461,7 +5842,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -99,7 +99,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +144,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F1F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -298,6 +308,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -995,9 +1017,9 @@
           <t>दृष्टि प्रतिशत</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>🟡 नियम मिल गए (प्रतिशत सहित) — पर शीट से 3 टकराव; 5 भावों का ज़िक्र नहीं।</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — आपके नियम अधिकृत, शीट ग़लत मानी गई। सूची पूरी सिद्ध (भाव 1-6 देखते हैं, 7-12 नहीं, 8 अपवाद)।</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1007,7 +1029,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>3 उप-सवाल</t>
+          <t>कोड में लगाना बाकी</t>
         </is>
       </c>
     </row>
@@ -1215,28 +1237,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🟠 दृष्टि — आसान विकल्प मौजूद</t>
+          <t>✅ दृष्टि नियम — अंतिम रूप से तय (आपके नियम अधिकृत)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>आपने नियम दोबारा वैसे ही भेजे ⇒ ये अंतिम माने गए। xlsx की bhav_drishti शीट ग़लत मानी गई (वह 'हर भाव +6' वाला सीधा गणित थी)।</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>✅ आपके दिए नियम (दर्ज) — दृष्टि एकतरफ़ा, आगे की ओर; पीछे नहीं देखती (8→2 अपवाद छोड़कर)</t>
-        </is>
-      </c>
+      <c r="A3" s="29" t="n"/>
+      <c r="B3" s="28" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="28" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1251,310 +1279,320 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>प्रतिशत</t>
+          <t>ताकत</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>xlsx शीट / मिलान</t>
+          <t>टिप्पणी</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>भाव 7</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>7 ✓ मेल</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>भाव 6</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>8 ✗ अलग</t>
-        </is>
-      </c>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>9, 11</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>भाव 9 , भाव 11</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>9 ◐ आंशिक</t>
-        </is>
-      </c>
+      <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>भाव 10</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>10 ✓ मेल</t>
-        </is>
-      </c>
+      <c r="D8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>भाव 9</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>11 ✗ अलग</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>भाव 12</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>12 ✓ मेल</t>
-        </is>
-      </c>
+      <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>100% (उल्टी/टक्कर)</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>2 ✓ मेल</t>
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>— कोई नहीं</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>आगे कोई भाव नहीं बचा</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>7, 9, 10, 11, 12</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>— आपके नियम में नहीं</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>भाव 2</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ अपवाद — पीछे मुड़कर। 'अचानक मार' / 'गुप्त नज़र' / 'टक्कर की दृष्टि' — अचानक भारी नुकसान</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>— कोई नहीं</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>शीट में +6 वाला भाव</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="n"/>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>आगे कोई भाव नहीं बचा</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>🔎 xlsx का drishti कॉलम सीधा गणित है — हर भाव अपने से 6 आगे वाले को देखता है। न प्रतिशत, न अपवाद।</t>
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>— कोई नहीं</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>आगे कोई भाव नहीं बचा</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ 3 टकराव — भाव 2 (आप 6 / शीट 8) · भाव 5 (आप 9 / शीट 11) · भाव 3 (आप 9+11 / शीट केवल 9)</t>
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>— कोई नहीं</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>आगे कोई भाव नहीं बचा</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>— कोई नहीं</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>आगे कोई भाव नहीं बचा</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>सवाल</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>विवरण</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>✏️ आपका उत्तर</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>सूची पूरी है?</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>भाव 7, 9, 10, 11, 12 — क्या ये किसी को नहीं देखते?</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr"/>
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>🔎 पुष्टि: भाव 1–6 — छहों दृष्टि डालते हैं · भाव 7–12 — कोई नहीं (सिवाय भाव 8 की उल्टी दृष्टि)। यह आपके 'एकतरफ़ा/आगे की ओर' नियम से पूरी तरह मेल खाता है ⇒ सूची पूरी है।</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>बुनियाद की पूरी सूची</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>आपने दो दिए: 9→5 की बुनियाद · 2→8 की बुनियाद। और जोड़े?</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>टकराव में किसे मानें</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>जहाँ आपका नियम व शीट अलग — हमेशा आपका नियम सही मानूँ?</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="28" t="n"/>
-      <c r="C21" s="28" t="n"/>
-      <c r="D21" s="28" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="28" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="28" t="n"/>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="28" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="n"/>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>बुनियाद (जड़) का नियम — दृष्टि से अलग</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>जड़ (बुनियाद)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>किसकी</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>असर</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>भाव 9</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>भाव 5 की</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>9वें में पापी/नीच ग्रह ⇒ 5वें में बैठे उच्च ग्रह का फल भी ख़राब</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>भाव 2</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>भाव 8 की</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2रे में शुभ ग्रह ⇒ 8वें के अशुभ परिणाम काफ़ी हद तक दब जाते हैं</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>और जोड़े हैं? (न हों तो खाली छोड़ दें — मैं इन्हीं दो को लगाऊँगा)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="28" t="n"/>
@@ -1562,12 +1600,97 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>📌 अभी सॉफ़्टवेयर में पुरानी '+6' तालिका चल रही है (2→8, 5→11 आदि, बिना प्रतिशत व अपवाद)। आपके 'अभी कुछ मत बनाओ' निर्देश के कारण कोड नहीं छुआ। कहें तो ऊपर वाली तालिका लगा दूँ — इससे 'सोया ग्रह' का नियम भी अपने-आप चालू हो जाएगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="28" t="n"/>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="n"/>
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C8:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4886,6 +5009,9 @@
           <t>✅ सोया ग्रह — परिभाषा</t>
         </is>
       </c>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="20" t="n"/>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -4893,6 +5019,9 @@
           <t>ग्रह भाव में बैठा है, पर जिस भाव को देखना चाहिए वह पूरी तरह खाली ⇒ सोया। उदा: सूर्य 1st में, 7th खाली ⇒ सूर्य सोया। असर: कोई फल नहीं — न अच्छा न बुरा। जागता है: ① उम्र से (शनि 36, राहु 42) ② कर्म से (नींव⇒शनि, विवाह⇒शुक्र)।</t>
         </is>
       </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="20" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -4900,6 +5029,9 @@
           <t>🔗 यह दृष्टि पर निर्भर है — दृष्टि का सवाल हल होते ही यह नियम चालू हो जाएगा।</t>
         </is>
       </c>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="20" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -4907,6 +5039,9 @@
           <t>🔴 चाहिए — सोया भाव जगाने की 'चाबी' तालिका</t>
         </is>
       </c>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="20" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -5781,6 +5916,11 @@
           <t>✅ मसनूई तालिका पूरी — सूर्य+शनि = मंगल बद (फल नीच राहु जैसा)। दस्तावेज़ का 'सूर्य+शनि = कृत्रिम राहु' वाला कथन असर की बात था, नाम की नहीं।</t>
         </is>
       </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="27" t="n"/>

--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -10,15 +10,16 @@
     <sheet name="STATUS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PAKKA_ANALYSIS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ANSWERED_UCHNEECH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ANSWERED_A2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ANSWERED_SUPT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ANSWERED_SOYA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="A_Pending" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Followups" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Masnui" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Drishti_Pct" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="B_C_Confirm" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Scope" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ANSWERED_KARAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ANSWERED_A2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ANSWERED_SUPT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ANSWERED_SOYA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="A_Pending" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Followups" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Masnui" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Drishti_Pct" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="B_C_Confirm" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Scope" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -685,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -747,9 +748,9 @@
           <t>पक्का / कच्चा घर</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🔴 फिर से खुला — आपका शक सही निकला। आपकी सूची में उच्च-घर, कारक-भाव व पक्के-घर मिले हुए हैं (प्रमाण शीट में)। साथ ही एक पुरानी गलती भी मिली।</t>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>🔴 केवल यही बड़ा बाकी — उच्च व कारक दोनों पुष्ट हो गए; अब शुद्ध पक्का/कच्चा सूची चाहिए।</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -882,9 +883,9 @@
           <t>सोया ग्रह — पहचान</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>🟡 दोनों परिभाषाएँ मिलीं (सोया भाव व सोया ग्रह) — बाकी: भाव जगाने की चाबी-तालिका।</t>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>✅ पूरा — सोया भाव व सोया ग्रह की परिभाषा + जगाने की पूरी चाबी तालिका (12 भाव) मिल गई।</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -894,7 +895,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>एक विकल्प चुनें</t>
+          <t>कुछ नहीं</t>
         </is>
       </c>
     </row>
@@ -1217,6 +1218,60 @@
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>कुछ नहीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>कारक ग्रह तालिका</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — 12 में से 11 पंक्तियाँ मेरे डेटा से मेल; भाव 6 में बुध जुड़ा, भाव 5 व 12 को सहायक मिले।</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ANSWERED_KARAK</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>कुछ नहीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>उच्च सूची</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>✅ आपने पुष्टि कर दी — मेरी सूची सही है।</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ANSWERED_UCHNEECH</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>कुछ नहीं</t>
         </is>
@@ -1232,6 +1287,453 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🟠 मसनूई (कृत्रिम) ग्रह तालिका</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>न भरें तो केवल सूर्य+शनि वाला नियम लगेगा — काम नहीं रुकेगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ग्रह 1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ग्रह 2</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>बनता है</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>स्थिति</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>शर्त</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>✅ टकराव सुलझा — यही मसनुई मंगल है</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>✅ सुधार — पहले 'सूर्य+बुध' लिखा था; सही है सूर्य+शुक्र</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>शनि (केतु-स्वभाव)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>शनि (राहु-स्वभाव)</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>राहु (उच्च)</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>केतु (उच्च)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>केतु (नीच)</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>मंगल (बद)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — फलादेश में 'नीच राहु' जैसा असर</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>🔴 बचा हुआ एक टकराव — सूर्य + शनि: आपने पहले 'मंगल (बद)' भी लिखा था और 'राहु (नीच)' भी। आपके नियम-दस्तावेज़ में 'सूर्य + शनि = कृत्रिम राहु' लिखा है, जो 'राहु (नीच)' से मेल खाता है। कृपया बताएँ — कौन सा सही है, या दोनों की अलग-अलग शर्त है?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>✅ मसनूई तालिका पूरी — सूर्य+शनि = मंगल बद (फल नीच राहु जैसा)। दस्तावेज़ का 'सूर्य+शनि = कृत्रिम राहु' वाला कथन असर की बात था, नाम की नहीं।</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"सूर्य,चन्द्र,मंगल,बुध,गुरु,शुक्र,शनि,राहु,केतु"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1516,6 +2018,9 @@
           <t>🔎 पुष्टि: भाव 1–6 — छहों दृष्टि डालते हैं · भाव 7–12 — कोई नहीं (सिवाय भाव 8 की उल्टी दृष्टि)। यह आपके 'एकतरफ़ा/आगे की ओर' नियम से पूरी तरह मेल खाता है ⇒ सूची पूरी है।</t>
         </is>
       </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="20" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="25" t="n"/>
@@ -1529,6 +2034,9 @@
           <t>बुनियाद (जड़) का नियम — दृष्टि से अलग</t>
         </is>
       </c>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="20" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1606,6 +2114,9 @@
           <t>📌 अभी सॉफ़्टवेयर में पुरानी '+6' तालिका चल रही है (2→8, 5→11 आदि, बिना प्रतिशत व अपवाद)। आपके 'अभी कुछ मत बनाओ' निर्देश के कारण कोड नहीं छुआ। कहें तो ऊपर वाली तालिका लगा दूँ — इससे 'सोया ग्रह' का नियम भी अपने-आप चालू हो जाएगा।</t>
         </is>
       </c>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="28" t="n"/>
@@ -1689,8 +2200,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C8:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1701,7 +2212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2000,7 +2511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2227,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3060,11 +3571,19 @@
       <c r="H35" s="19" t="n"/>
       <c r="I35" s="20" t="n"/>
     </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>🔄 अद्यतन: अब उच्च व कारक — दोनों तालिकाएँ आपने पुष्ट कर दी हैं। इनसे विश्लेषण दोबारा चलाया — बचे हुए भाव वही रहे: सूर्य 9,10 · मंगल 1,11 · बुध 2,5 · शुक्र 4 · शनि 3,11 · राहु 11 · (चन्द्र, गुरु, केतु — कुछ नहीं बचा)। अब केवल शुद्ध पक्का/कच्चा सूची बाकी है।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A37:I37"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A35:I35"/>
@@ -3903,6 +4422,406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>✅ 12 भावों के कारक ग्रह — तय (आपकी तालिका)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>आपकी तालिका मेरे डेटा से 12 में से 11 पंक्तियों पर हूबहू मिलती है। केवल भाव 6 में बुध जुड़ा, और भाव 5 व 12 को 'सहायक' ग्रह मिले।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>भाव</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>कारक ग्रह (आपका)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>सहायक</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>मेरा पुराना डेटा</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>मिलान</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>भाव 1</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>भाव 2</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>भाव 3</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>भाव 4</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>भाव 5</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>भाव 6</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>केतु और बुध</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>🔵 बुध नया जुड़ा</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>भाव 7</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र और बुध</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>बुध, शुक्र</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>भाव 8</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>शनि और मंगल</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>मंगल, शनि</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>भाव 9</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>भाव 10</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>भाव 11</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>भाव 12</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>✓ मेल</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>ग्रह-अनुसार (पलटकर): सूर्य 1 · चन्द्र 4 · मंगल 3,8 · बुध 6,7 · गुरु 2,5,9,11 · शुक्र 7 · शनि 8,10 · राहु 12 · केतु 6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4653,7 +5572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4906,13 +5825,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4928,6 +5847,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -4942,6 +5862,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
@@ -5003,6 +5924,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr"/>
     </row>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -5033,6 +5955,7 @@
       <c r="C13" s="19" t="n"/>
       <c r="D13" s="20" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -5043,48 +5966,45 @@
       <c r="C15" s="19" t="n"/>
       <c r="D15" s="20" t="n"/>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>✅ सोया भाव जगाने की 'चाबी' तालिका — पूरी (आपकी दी हुई)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>सोया भाव</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>जगाने वाला भाव (चाबी)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>स्थिति</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>भाव 1</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>जगाने वाला 'चाबी' भाव</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>किस ग्रह से जागेगा</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>भाव 2</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 1</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>7वां</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -5092,13 +6012,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>भाव 3</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 2</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>9वां</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -5106,13 +6030,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>भाव 4</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 3</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>11वां</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -5120,13 +6048,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>भाव 5</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 4</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>10वां</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>शनि</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -5134,13 +6066,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>भाव 6</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 5</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>9वां</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -5148,13 +6084,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>भाव 7</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 6</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>2रा</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -5162,13 +6102,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>भाव 8</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 7</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>1ला</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>मंगल</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
@@ -5176,17 +6120,17 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>भाव 9 (भाग्य)</t>
+          <t>भाव 8</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>भाव 2 (धर्मस्थान/कुटुंब)</t>
+          <t>2रा</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>✅ आपने बताया</t>
+          <t>गुरु</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -5194,13 +6138,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>भाव 10</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 9</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>2रा</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>गुरु</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
@@ -5208,13 +6156,17 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>भाव 11</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
+          <t>भाव 10</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>4था</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -5222,22 +6174,59 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>भाव 11</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>3रा</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>भाव 12</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>चाहिए</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>6ठा</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>बुध या केतु</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>🔎 पैटर्न: चार जोड़े आपस में एक-दूसरे की चाबी हैं — 1↔7 · 4↔10 · 3↔11 · 2↔9। बाकी एकतरफ़ा (5→9, 6→2, 8→2, 12→6)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="28" t="n"/>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
@@ -5245,7 +6234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5402,7 +6391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5544,451 +6533,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>🟠 मसनूई (कृत्रिम) ग्रह तालिका</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>न भरें तो केवल सूर्य+शनि वाला नियम लगेगा — काम नहीं रुकेगा।</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ग्रह 1</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ग्रह 2</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>बनता है</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>स्थिति</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>शर्त</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>बुध</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>बुध</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>मंगल</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>✅ टकराव सुलझा — यही मसनुई मंगल है</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>गुरु</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>✅ सुधार — पहले 'सूर्य+बुध' लिखा था; सही है सूर्य+शुक्र</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>गुरु</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>राहु</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>बुध</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>राहु</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>केतु</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>गुरु</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>शनि (केतु-स्वभाव)</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>मंगल</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>बुध</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>शनि (राहु-स्वभाव)</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>मंगल</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>राहु (उच्च)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>शुक्र</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>केतु (उच्च)</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>चन्द्र</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>केतु (नीच)</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>सूर्य</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>शनि</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>मंगल (बद)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>✅ तय — फलादेश में 'नीच राहु' जैसा असर</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>🔴 बचा हुआ एक टकराव — सूर्य + शनि: आपने पहले 'मंगल (बद)' भी लिखा था और 'राहु (नीच)' भी। आपके नियम-दस्तावेज़ में 'सूर्य + शनि = कृत्रिम राहु' लिखा है, जो 'राहु (नीच)' से मेल खाता है। कृपया बताएँ — कौन सा सही है, या दोनों की अलग-अलग शर्त है?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>✅ मसनूई तालिका पूरी — सूर्य+शनि = मंगल बद (फल नीच राहु जैसा)। दस्तावेज़ का 'सूर्य+शनि = कृत्रिम राहु' वाला कथन असर की बात था, नाम की नहीं।</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="20" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="27" t="n"/>
-      <c r="B19" s="28" t="n"/>
-      <c r="C19" s="28" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="28" t="n"/>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:F18"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"सूर्य,चन्द्र,मंगल,बुध,गुरु,शुक्र,शनि,राहु,केतु"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/LALKITAB_INFO_REQUEST_v3.xlsx
+++ b/docs/LALKITAB_INFO_REQUEST_v3.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="STATUS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PAKKA_ANALYSIS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ANSWERED_UCHNEECH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ANSWERED_KARAK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ANSWERED_A2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ANSWERED_SUPT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ANSWERED_SOYA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="A_Pending" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Followups" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Masnui" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Drishti_Pct" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="B_C_Confirm" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Scope" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ANSWERED_PAKKA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PAKKA_ANALYSIS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ANSWERED_UCHNEECH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ANSWERED_KARAK" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ANSWERED_A2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ANSWERED_SUPT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ANSWERED_SOYA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="A_Pending" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Followups" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Masnui" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Drishti_Pct" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="B_C_Confirm" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Scope" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -748,19 +749,19 @@
           <t>पक्का / कच्चा घर</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>🔴 केवल यही बड़ा बाकी — उच्च व कारक दोनों पुष्ट हो गए; अब शुद्ध पक्का/कच्चा सूची चाहिए।</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>✅ हल — पक्का घर = कारक भाव (एक ही तालिका)। मास्टर तालिका दर्ज। केवल 'कच्चा घर' अनुमानित है।</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>PAKKA_ANALYSIS</t>
+          <t>ANSWERED_PAKKA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>शुद्ध सूची दें</t>
+          <t>कुछ नहीं</t>
         </is>
       </c>
     </row>
@@ -910,9 +911,9 @@
           <t>वर्षफल विधि</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>🔴 बाकी</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>✅ तय — दोनों तरीके (A से चार्ट + B की परत) और असली गोचर भी जोड़ें।</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -922,7 +923,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>एक विकल्प चुनें</t>
+          <t>कुछ नहीं</t>
         </is>
       </c>
     </row>
@@ -1287,6 +1288,150 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🔴 छोटे सवाल</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>विषय</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>सवाल</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>मेरा प्रस्ताव</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>आपका उत्तर</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>टिप्पणी</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>आयु गिनने का तरीका ⭐</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>दशा में 'शनि 1 से 6 वर्ष' — (क) जन्म से 6ठे जन्मदिन तक, यानी पूर्ण आयु 0–5 (जीवन का पहला वर्ष = 1); या (ख) पूर्ण आयु 1 से 6? इससे पूरी दशा एक वर्ष खिसक जाती है।</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>(क) जीवन-वर्ष — नवजात 'वर्ष 1' में</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✅ उत्तर मिला — (क) सही</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>जीवन का 1st वर्ष = जन्म→पहला जन्मदिन = Completed Age 0। शनि 1–6 वर्ष = Completed Age 0–5। यही मैंने लगाया था — बदलाव नहीं चाहिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>grah_chakra के बाकी कॉलम</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>'प्रभाव' कॉलम गलत निकला। उसी शीट के 'अशुभ' (सावधानी-वर्ष) व 'विशेष' कॉलम अभी भी उपयोग में हैं — भरोसेमंद हैं?</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>पुष्टि तक 'अपुष्ट' चिह्नित रखूँ</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ग्रह-संख्या की पुष्टि</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>सूर्य 1, चन्द्र 2, मंगल 9, बुध 5, गुरु 3, शुक्र 6, शनि 8, राहु 18, केतु 7 — क्या ये लाल किताब के अंक हैं? राहु 18 = दान-मात्रा?</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>केवल दान-मात्रा में उपयोग करूँ</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1733,7 +1878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2212,7 +2357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2511,7 +2656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2733,6 +2878,423 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>✅ पक्का घर — हल हो गया (पक्का घर = कारक भाव)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>आपका निष्कर्ष: “प्रत्येक भाव का एक कारक ग्रह होता है, और वही भाव उस ग्रह का पक्का घर कहलाता है। अर्थात् पक्का घर और कारक भाव — दोनों एक ही तालिका हैं, दो नहीं।”</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>पक्के घर का अर्थ: ग्रह अपने पक्के घर में हो तो 'पूरी तरह जागता हुआ' — दूसरे भाव/ग्रह को प्रभावित करने में पूर्ण समर्थ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ग्रह</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>पक्का घर (= कारक)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>स्वराशि भाव</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>कच्चा घर (अनुमानित)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>उच्च</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>नीच</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>सूर्य</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>5 (सिंह)</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>चन्द्र</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>4 (कर्क)</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>मंगल</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>3, 8</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1, 8</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>बुध</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>6, 7</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>3, 6</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>गुरु</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>2, 5, 9, 11, 12</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>9, 12</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>शुक्र</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2, 7</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>शनि</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>8, 10</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>राहु</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>12 (मीन)</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>3, 6</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>9, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>केतु</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>6 (कन्या)</t>
+        </is>
+      </c>
+      <c r="E15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>9, 12</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>3, 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>✔ नीच भाव = उच्च भाव से सातवाँ — नौ के नौ ग्रहों पर सटीक बैठता है (जाँच लिया)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ 'कच्चा घर' — आपकी फ़ाइल में ही लिखा है कि इसकी कोई मानक शास्त्रीय सूची स्रोतों में नहीं मिली; यह गृहफल/राशिफल सिद्धांत से निकाला तार्किक अर्थ है (= स्वराशि भाव जो कारक भाव नहीं)। मैं इसे लगाऊँगा पर स्क्रीन पर 'अनुमानित' लिखा रहेगा।</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3577,6 +4139,14 @@
           <t>🔄 अद्यतन: अब उच्च व कारक — दोनों तालिकाएँ आपने पुष्ट कर दी हैं। इनसे विश्लेषण दोबारा चलाया — बचे हुए भाव वही रहे: सूर्य 9,10 · मंगल 1,11 · बुध 2,5 · शुक्र 4 · शनि 3,11 · राहु 11 · (चन्द्र, गुरु, केतु — कुछ नहीं बचा)। अब केवल शुद्ध पक्का/कच्चा सूची बाकी है।</t>
         </is>
       </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3594,7 +4164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4416,7 +4986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4446,6 +5016,11 @@
           <t>आपकी तालिका मेरे डेटा से 12 में से 11 पंक्तियों पर हूबहू मिलती है। केवल भाव 6 में बुध जुड़ा, और भाव 5 व 12 को 'सहायक' ग्रह मिले।</t>
         </is>
       </c>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="n"/>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="20" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -4805,6 +5380,11 @@
           <t>ग्रह-अनुसार (पलटकर): सूर्य 1 · चन्द्र 4 · मंगल 3,8 · बुध 6,7 · गुरु 2,5,9,11 · शुक्र 7 · शनि 8,10 · राहु 12 · केतु 6</t>
         </is>
       </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4816,7 +5396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5572,7 +6152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5825,7 +6405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5847,7 +6427,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -5862,7 +6441,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
@@ -5924,7 +6502,6 @@
       </c>
       <c r="D9" s="8" t="inlineStr"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -5955,7 +6532,6 @@
       <c r="C13" s="19" t="n"/>
       <c r="D13" s="20" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -5972,6 +6548,9 @@
           <t>✅ सोया भाव जगाने की 'चाबी' तालिका — पूरी (आपकी दी हुई)</t>
         </is>
       </c>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="20" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -6213,6 +6792,9 @@
           <t>🔎 पैटर्न: चार जोड़े आपस में एक-दूसरे की चाबी हैं — 1↔7 · 4↔10 · 3↔11 · 2↔9। बाकी एकतरफ़ा (5→9, 6→2, 8→2, 12→6)।</t>
         </is>
       </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="28" t="n"/>
@@ -6234,7 +6816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6343,7 +6925,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
     </row>
-    <row r="6" ht="86" customHeight="1">
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>A4</t>
@@ -6374,8 +6956,16 @@
           <t>दोनों: permutation = चार्ट, overlay = फल। (+ असली गोचर जोड़ें? हाँ/नहीं)</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>F + असली गोचर</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>✅ दोनों तरीके — A से चार्ट, B की परत, और उस वर्ष की असली गोचर स्थिति भी</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6389,148 +6979,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>🔴 छोटे सवाल</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>विषय</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>सवाल</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>मेरा प्रस्ताव</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>आपका उत्तर</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>टिप्पणी</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>आयु गिनने का तरीका ⭐</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>दशा में 'शनि 1 से 6 वर्ष' — (क) जन्म से 6ठे जन्मदिन तक, यानी पूर्ण आयु 0–5 (जीवन का पहला वर्ष = 1); या (ख) पूर्ण आयु 1 से 6? इससे पूरी दशा एक वर्ष खिसक जाती है।</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>(क) जीवन-वर्ष — नवजात 'वर्ष 1' में</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>✅ उत्तर मिला — (क) सही</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>जीवन का 1st वर्ष = जन्म→पहला जन्मदिन = Completed Age 0। शनि 1–6 वर्ष = Completed Age 0–5। यही मैंने लगाया था — बदलाव नहीं चाहिए।</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>grah_chakra के बाकी कॉलम</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>'प्रभाव' कॉलम गलत निकला। उसी शीट के 'अशुभ' (सावधानी-वर्ष) व 'विशेष' कॉलम अभी भी उपयोग में हैं — भरोसेमंद हैं?</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>पुष्टि तक 'अपुष्ट' चिह्नित रखूँ</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>ग्रह-संख्या की पुष्टि</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>सूर्य 1, चन्द्र 2, मंगल 9, बुध 5, गुरु 3, शुक्र 6, शनि 8, राहु 18, केतु 7 — क्या ये लाल किताब के अंक हैं? राहु 18 = दान-मात्रा?</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>केवल दान-मात्रा में उपयोग करूँ</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>